--- a/data/trans_orig/IP11B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP11B-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>538</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13981</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22407</t>
+          <t>22285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15783</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19118</t>
+          <t>18801</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18283</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4154,12 +4154,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>36636</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>61619</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17483</t>
+          <t>17495</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -5848,12 +5848,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5863,12 +5863,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -5961,12 +5961,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15849</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>15175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>23504</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6011,12 +6011,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27447</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37803</t>
+          <t>38234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -6756,12 +6756,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>17165</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,74%</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -7551,12 +7551,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>11949</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>21133</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>29647</t>
+          <t>29747</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7699,12 +7699,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -8233,12 +8233,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>33557</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>43776</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>40474</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>54533</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>77831</t>
+          <t>78895</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>95441</t>
+          <t>94970</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8642,12 +8642,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8657,12 +8657,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -10168,12 +10168,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12181</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -10281,12 +10281,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10366,12 +10366,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11033,12 +11033,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11048,12 +11048,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11259,12 +11259,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11715,12 +11715,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11730,12 +11730,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -11758,12 +11758,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11773,12 +11773,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19071</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11921,12 +11921,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11956,12 +11956,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12054,12 +12054,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12475,12 +12475,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12490,12 +12490,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12525,12 +12525,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12588,12 +12588,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32129</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>34325</t>
+          <t>34277</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46961</t>
+          <t>46974</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12638,12 +12638,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12681,12 +12681,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12716,12 +12716,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12751,12 +12751,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -12779,12 +12779,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -14154,7 +14154,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -14267,7 +14267,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>415</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -14410,12 +14410,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14425,12 +14425,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14445,12 +14445,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14460,12 +14460,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,6%</t>
         </is>
       </c>
     </row>
@@ -14493,7 +14493,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14508,7 +14508,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14558,12 +14558,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15127,12 +15127,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>399</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15142,12 +15142,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -15170,7 +15170,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15318,12 +15318,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>352</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15333,12 +15333,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15353,12 +15353,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>741</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15368,12 +15368,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -15744,7 +15744,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15892,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -15965,12 +15965,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15980,12 +15980,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16000,12 +16000,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16015,12 +16015,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16035,12 +16035,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14234</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16050,12 +16050,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>81,26%</t>
         </is>
       </c>
     </row>
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16113,12 +16113,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16128,12 +16128,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16148,12 +16148,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16163,12 +16163,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -16534,12 +16534,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16549,12 +16549,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16604,12 +16604,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16619,12 +16619,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -16682,12 +16682,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -16697,12 +16697,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -16717,12 +16717,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16732,12 +16732,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -16760,12 +16760,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16775,12 +16775,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16795,12 +16795,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>16847</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16810,12 +16810,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16830,12 +16830,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16845,12 +16845,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -16873,12 +16873,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16888,12 +16888,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16908,12 +16908,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16943,12 +16943,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16958,12 +16958,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
